--- a/RSI Modular - copia/tabla_maestra_BVSP.xlsx
+++ b/RSI Modular - copia/tabla_maestra_BVSP.xlsx
@@ -545,28 +545,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.74</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.85</v>
+        <v>-1.11</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.59</v>
+        <v>-2.28</v>
       </c>
       <c r="K3" t="n">
-        <v>0.52</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="4">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E4" t="n">
         <v>0.08</v>
@@ -1119,28 +1119,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>42.1</v>
+        <v>38.9</v>
       </c>
       <c r="F3" t="n">
-        <v>42.1</v>
+        <v>44.4</v>
       </c>
       <c r="G3" t="n">
-        <v>36.8</v>
+        <v>33.3</v>
       </c>
       <c r="H3" t="n">
-        <v>47.4</v>
+        <v>44.4</v>
       </c>
       <c r="I3" t="n">
-        <v>36.8</v>
+        <v>33.3</v>
       </c>
       <c r="J3" t="n">
-        <v>50</v>
+        <v>47.1</v>
       </c>
       <c r="K3" t="n">
-        <v>56.2</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="4">
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E4" t="n">
         <v>55.6</v>
@@ -1222,7 +1222,7 @@
         <v>37</v>
       </c>
       <c r="K5" t="n">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="6">
@@ -1687,11 +1687,15 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -1714,7 +1718,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
